--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98607</v>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124453</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33546-2025 artfynd.xlsx
+++ b/artfynd/A 33546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128124453</v>
+        <v>69768026</v>
       </c>
       <c r="B2" t="n">
-        <v>98614</v>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ryttarkärret, Ryttarkärret, Upl</t>
+          <t>Nordängen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697955</v>
+        <v>697977</v>
       </c>
       <c r="R2" t="n">
-        <v>6640895</v>
+        <v>6640823</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På block.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,15 +768,411 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69768037</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nordängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>697977</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6640823</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På block.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128124142</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ryttarkärret, Ryttarkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>698039</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6640870</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128124366</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ryttarkärret, Ryttarkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698009</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6640931</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128124453</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ryttarkärret, Ryttarkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>697955</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6640895</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
